--- a/isms-core-framework/A.8-technological-controls/isms-a.8.25-26-29-secure-development/WKBK/90_workbooks/ISMS-IMP-A.8.25-26-29.S1_Security_Requirements_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.25-26-29-secure-development/WKBK/90_workbooks/ISMS-IMP-A.8.25-26-29.S1_Security_Requirements_Assessment_20260208.xlsx
@@ -1337,7 +1337,7 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>GDPR, PCI DSS</t>
+          <t>GDPR, PCI DSS v4.0.1</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
